--- a/case-directory.xlsx
+++ b/case-directory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\macristina.magdamit\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7210C686-DD9F-4083-9B2B-5E187CC4FC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18158C0-E560-4043-98DA-775505B15EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="268">
   <si>
     <t>QUEUE/ Request</t>
   </si>
@@ -5440,440 +5440,7 @@
     </r>
   </si>
   <si>
-    <t>LG Electronics</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>ALL DISPUTES from/for </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>LG</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t> (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>@lge.com</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>, </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>@lgcns </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>or </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>@cnspartner.com</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>) should be moved to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>Errold David</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t> who will preprocess/PPP the case</t>
-    </r>
-  </si>
-  <si>
-    <t>Move the Case except if assigned by Errold to other queue</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">To Errold
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>• Assign cases with subjects below to your name under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">FXF Billing Disputes
-  "LG UNMATCHED"
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>"US_DAILY_OPEN_INVOICE_FXFE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>"
-   "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>RETURN</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>" (related to return Load IDs)
-• For other cases, assign to the appropriate queue
-ALL Cases from/for LG
-Case Owner: Errold David
-Case Origin: WRO Main Invoicing
-Sub Queue: NO SUB-QUEUE</t>
-    </r>
-  </si>
-  <si>
     <t>Ryder</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ALL Cases from/for RYDER with the following Subject
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>Case Owner: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Angelito Pineda
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>Case Origin: WRO Main Invoicing
-Sub Queue: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">NO SUB-QUEUE
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-TO EVERYONE </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>Anything that Angelito assigns to another queue should not be moved back to him</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>Disputes with the following Subject should be moved to </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>Angelito Pineda</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> who will preprocess/PPP the case.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>"Ryder Weekly Cut Bills"
-"Freight Bill Reject Notification"
-"Ryder Weekly Rejected Bills"
-Other case with different subject for Ryder should be assign to regular queues based on Dispute(Billing Disput, Pricing, Reweigh, Inspection, SBL)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">To Angel
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>• Assign cases with subject </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>"Freight bill reject notification</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>" to your name under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">FXF Billing Disputes
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>• Assign cases with subject </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>"Ryder Weekly Cut Bills</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t>" to your name under </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Pricing 10 Pros or Less
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">• For other cases, assign to the appropriate queue
-</t>
-    </r>
   </si>
   <si>
     <t>Nolan &amp; Cunnings</t>
@@ -7987,6 +7554,217 @@
       </rPr>
       <t>to your name under FXF Billing Disputes or Pricing 10 Pros or less, depending on the dispute types
 • For other cases, assign to the appropriate queue</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Disputes with the following Subject should be moved to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Joselito Apog </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">who will preprocess/PPP the case.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>"Ryder Weekly Cut Bills"
+"Freight Bill Reject Notification"
+"Ryder Weekly Rejected Bills"
+Other case with different subject for Ryder should be assign to regular queues based on Dispute(Billing Disput, Pricing, Reweigh, Inspection, SBL)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">To Joselito
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>• Assign cases with subject </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>"Freight bill reject notification</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>" to your name under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">FXF Billing Disputes
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>• Assign cases with subject </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>"Ryder Weekly Cut Bills</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>" to your name under </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Pricing 10 Pros or Less
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">• For other cases, assign to the appropriate queue
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">ALL Cases from/for RYDER with the following Subject
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Case Owner: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Joselito Apog
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Case Origin: WRO Main Invoicing
+Sub Queue: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">NO SUB-QUEUE
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+TO EVERYONE </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Anything that Joselito assigns to another queue should not be moved back to him</t>
     </r>
   </si>
 </sst>
@@ -8705,7 +8483,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9001,18 +8779,6 @@
     <xf numFmtId="0" fontId="71" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="69" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9066,6 +8832,9 @@
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -9100,8 +8869,8 @@
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>1346835</xdr:colOff>
-      <xdr:row>1527</xdr:row>
-      <xdr:rowOff>8707</xdr:rowOff>
+      <xdr:row>1536</xdr:row>
+      <xdr:rowOff>171993</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9150,8 +8919,8 @@
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>2173605</xdr:colOff>
-      <xdr:row>1527</xdr:row>
-      <xdr:rowOff>68035</xdr:rowOff>
+      <xdr:row>1537</xdr:row>
+      <xdr:rowOff>46264</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9200,8 +8969,8 @@
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>887730</xdr:colOff>
-      <xdr:row>1576</xdr:row>
-      <xdr:rowOff>170155</xdr:rowOff>
+      <xdr:row>1586</xdr:row>
+      <xdr:rowOff>148384</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9250,8 +9019,8 @@
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>3192780</xdr:colOff>
-      <xdr:row>1527</xdr:row>
-      <xdr:rowOff>149950</xdr:rowOff>
+      <xdr:row>1537</xdr:row>
+      <xdr:rowOff>128179</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9817,10 +9586,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:F78"/>
+  <dimension ref="A3:F77"/>
   <sheetFormatPr defaultColWidth="33.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.21875" style="118" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.21875" style="114" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="88.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="71" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38" customWidth="1"/>
@@ -9851,13 +9620,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>7</v>
@@ -9920,16 +9689,16 @@
     </row>
     <row r="8" spans="1:6" ht="145.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="B8" s="112" t="s">
-        <v>262</v>
+        <v>253</v>
+      </c>
+      <c r="B8" s="108" t="s">
+        <v>255</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="F8" s="4"/>
     </row>
@@ -9973,8 +9742,8 @@
       <c r="A11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="114" t="s">
-        <v>263</v>
+      <c r="B11" s="110" t="s">
+        <v>256</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>24</v>
@@ -9989,11 +9758,11 @@
       <c r="A12" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B12" s="113" t="s">
-        <v>264</v>
+      <c r="B12" s="109" t="s">
+        <v>257</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="20" t="s">
@@ -10204,19 +9973,19 @@
       <c r="F24" s="4"/>
     </row>
     <row r="25" spans="1:6" ht="408.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="115" t="s">
+      <c r="A25" s="111" t="s">
         <v>80</v>
       </c>
-      <c r="B25" s="111" t="s">
+      <c r="B25" s="107" t="s">
         <v>81</v>
       </c>
-      <c r="C25" s="108" t="s">
+      <c r="C25" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="D25" s="109" t="s">
+      <c r="D25" s="105" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="110" t="s">
+      <c r="E25" s="106" t="s">
         <v>84</v>
       </c>
       <c r="F25" s="41"/>
@@ -10317,8 +10086,8 @@
       <c r="C31" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="119"/>
-      <c r="E31" s="120" t="s">
+      <c r="D31" s="115"/>
+      <c r="E31" s="116" t="s">
         <v>108</v>
       </c>
       <c r="F31" s="4"/>
@@ -10333,8 +10102,8 @@
       <c r="C32" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="119"/>
-      <c r="E32" s="120"/>
+      <c r="D32" s="115"/>
+      <c r="E32" s="116"/>
       <c r="F32" s="41"/>
     </row>
     <row r="33" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
@@ -10834,7 +10603,7 @@
       <c r="F62" s="4"/>
     </row>
     <row r="63" spans="1:6" ht="138" x14ac:dyDescent="0.3">
-      <c r="A63" s="116" t="s">
+      <c r="A63" s="112" t="s">
         <v>215</v>
       </c>
       <c r="B63" s="85" t="s">
@@ -10850,7 +10619,7 @@
       <c r="F63" s="4"/>
     </row>
     <row r="64" spans="1:6" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A64" s="116" t="s">
+      <c r="A64" s="112" t="s">
         <v>218</v>
       </c>
       <c r="B64" s="86" t="s">
@@ -10866,7 +10635,7 @@
       <c r="F64" s="4"/>
     </row>
     <row r="65" spans="1:6" ht="303.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A65" s="117" t="s">
+      <c r="A65" s="113" t="s">
         <v>221</v>
       </c>
       <c r="B65" s="88" t="s">
@@ -10882,18 +10651,18 @@
       <c r="F65" s="4"/>
     </row>
     <row r="66" spans="1:6" ht="386.4" x14ac:dyDescent="0.3">
-      <c r="A66" s="116" t="s">
+      <c r="A66" s="112" t="s">
         <v>225</v>
       </c>
       <c r="B66" s="89" t="s">
         <v>226</v>
       </c>
       <c r="C66" s="90" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D66" s="90"/>
       <c r="E66" s="50" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F66" s="91"/>
     </row>
@@ -10905,11 +10674,11 @@
         <v>225</v>
       </c>
       <c r="C67" s="90" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D67" s="90"/>
       <c r="E67" s="50" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F67" s="91"/>
     </row>
@@ -10921,11 +10690,11 @@
         <v>229</v>
       </c>
       <c r="C68" s="90" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D68" s="90"/>
       <c r="E68" s="50" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F68" s="91"/>
     </row>
@@ -10937,11 +10706,11 @@
         <v>231</v>
       </c>
       <c r="C69" s="90" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D69" s="90"/>
       <c r="E69" s="50" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F69" s="91"/>
     </row>
@@ -10953,11 +10722,11 @@
         <v>233</v>
       </c>
       <c r="C70" s="90" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D70" s="90"/>
       <c r="E70" s="50" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F70" s="91"/>
     </row>
@@ -10969,11 +10738,11 @@
         <v>235</v>
       </c>
       <c r="C71" s="90" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D71" s="90"/>
       <c r="E71" s="36" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="F71" s="91"/>
     </row>
@@ -10985,11 +10754,11 @@
         <v>237</v>
       </c>
       <c r="C72" s="90" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D72" s="90"/>
       <c r="E72" s="50" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="F72" s="91"/>
     </row>
@@ -11009,85 +10778,69 @@
       </c>
       <c r="F73" s="4"/>
     </row>
-    <row r="74" spans="1:6" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" ht="212.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="94" t="s">
         <v>242</v>
       </c>
-      <c r="B74" s="99" t="s">
-        <v>243</v>
-      </c>
-      <c r="C74" s="100" t="s">
-        <v>244</v>
-      </c>
-      <c r="D74" s="101"/>
-      <c r="E74" s="98" t="s">
-        <v>245</v>
+      <c r="B74" s="117" t="s">
+        <v>267</v>
+      </c>
+      <c r="C74" s="102" t="s">
+        <v>265</v>
+      </c>
+      <c r="D74" s="97"/>
+      <c r="E74" s="99" t="s">
+        <v>266</v>
       </c>
       <c r="F74" s="4"/>
     </row>
-    <row r="75" spans="1:6" ht="212.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="94" t="s">
-        <v>246</v>
-      </c>
-      <c r="B75" s="102" t="s">
-        <v>247</v>
-      </c>
-      <c r="C75" s="96" t="s">
-        <v>248</v>
+        <v>243</v>
+      </c>
+      <c r="B75" s="94" t="s">
+        <v>244</v>
+      </c>
+      <c r="C75" s="100" t="s">
+        <v>24</v>
       </c>
       <c r="D75" s="97"/>
-      <c r="E75" s="103" t="s">
-        <v>249</v>
+      <c r="E75" s="101" t="s">
+        <v>245</v>
       </c>
       <c r="F75" s="4"/>
     </row>
-    <row r="76" spans="1:6" ht="118.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" ht="194.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="94" t="s">
-        <v>250</v>
-      </c>
-      <c r="B76" s="94" t="s">
-        <v>251</v>
-      </c>
-      <c r="C76" s="104" t="s">
-        <v>24</v>
+        <v>246</v>
+      </c>
+      <c r="B76" s="102" t="s">
+        <v>262</v>
+      </c>
+      <c r="C76" s="95" t="s">
+        <v>263</v>
       </c>
       <c r="D76" s="97"/>
-      <c r="E76" s="105" t="s">
-        <v>252</v>
+      <c r="E76" s="99" t="s">
+        <v>264</v>
       </c>
       <c r="F76" s="4"/>
     </row>
-    <row r="77" spans="1:6" ht="194.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="134.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="94" t="s">
-        <v>253</v>
-      </c>
-      <c r="B77" s="106" t="s">
-        <v>269</v>
-      </c>
-      <c r="C77" s="95" t="s">
-        <v>270</v>
+        <v>247</v>
+      </c>
+      <c r="B77" s="96" t="s">
+        <v>248</v>
+      </c>
+      <c r="C77" s="103" t="s">
+        <v>249</v>
       </c>
       <c r="D77" s="97"/>
-      <c r="E77" s="103" t="s">
-        <v>271</v>
+      <c r="E77" s="99" t="s">
+        <v>250</v>
       </c>
       <c r="F77" s="4"/>
-    </row>
-    <row r="78" spans="1:6" ht="134.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="94" t="s">
-        <v>254</v>
-      </c>
-      <c r="B78" s="96" t="s">
-        <v>255</v>
-      </c>
-      <c r="C78" s="107" t="s">
-        <v>256</v>
-      </c>
-      <c r="D78" s="97"/>
-      <c r="E78" s="103" t="s">
-        <v>257</v>
-      </c>
-      <c r="F78" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/case-directory.xlsx
+++ b/case-directory.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\macristina.magdamit\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18158C0-E560-4043-98DA-775505B15EB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91E727D8-7854-43F5-9D06-DA90E93AF5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5446,118 +5446,6 @@
     <t>Nolan &amp; Cunnings</t>
   </si>
   <si>
-    <r>
-      <t>ALL Cases from/for NOLANS &amp; CUNNINGS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-Case Owner: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>Camille Ocampo</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-Case Origin: WRO Main Invoicing
-Sub Queue: </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>NO SUB-QUEUE</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-TO EVERYONE -</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <i/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t> Anything that Camille assigns to another queue should not be moved back to her</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>To Camille</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">
-• Assign cases with subject </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>"Daily Rejected Bills listing for mm/dd/yyyy</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t>" to your name under FXF Billing Disputes or Pricing 10 Pros or less, depending on the dispute types
-• For other cases, assign to the appropriate queue</t>
-    </r>
-  </si>
-  <si>
     <t>3M</t>
   </si>
   <si>
@@ -7765,6 +7653,117 @@
         <family val="2"/>
       </rPr>
       <t>Anything that Joselito assigns to another queue should not be moved back to him</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ALL Cases from/for NOLANS &amp; CUNNINGS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Case Owner: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>Mariel Guevarra</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Case Origin: WRO Main Invoicing
+Sub Queue: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>NO SUB-QUEUE</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+TO EVERYONE -</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t> Anything that Mariel assigns to another queue should not be moved back to her</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>To Mariel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+• Assign cases with subject </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>"Daily Rejected Bills listing for mm/dd/yyyy</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t>" to your name under FXF Billing Disputes or Pricing 10 Pros or less, depending on the dispute types
+• For other cases, assign to the appropriate queue</t>
     </r>
   </si>
 </sst>
@@ -8827,14 +8826,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="40" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -9620,13 +9619,13 @@
         <v>5</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E4" s="9" t="s">
         <v>7</v>
@@ -9689,16 +9688,16 @@
     </row>
     <row r="8" spans="1:6" ht="145.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B8" s="108" t="s">
         <v>253</v>
-      </c>
-      <c r="B8" s="108" t="s">
-        <v>255</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>24</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F8" s="4"/>
     </row>
@@ -9743,7 +9742,7 @@
         <v>31</v>
       </c>
       <c r="B11" s="110" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>24</v>
@@ -9759,10 +9758,10 @@
         <v>33</v>
       </c>
       <c r="B12" s="109" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="20" t="s">
@@ -10086,8 +10085,8 @@
       <c r="C31" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="D31" s="115"/>
-      <c r="E31" s="116" t="s">
+      <c r="D31" s="116"/>
+      <c r="E31" s="117" t="s">
         <v>108</v>
       </c>
       <c r="F31" s="4"/>
@@ -10102,8 +10101,8 @@
       <c r="C32" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="D32" s="115"/>
-      <c r="E32" s="116"/>
+      <c r="D32" s="116"/>
+      <c r="E32" s="117"/>
       <c r="F32" s="41"/>
     </row>
     <row r="33" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
@@ -10658,11 +10657,11 @@
         <v>226</v>
       </c>
       <c r="C66" s="90" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D66" s="90"/>
       <c r="E66" s="50" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F66" s="91"/>
     </row>
@@ -10674,11 +10673,11 @@
         <v>225</v>
       </c>
       <c r="C67" s="90" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D67" s="90"/>
       <c r="E67" s="50" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F67" s="91"/>
     </row>
@@ -10690,11 +10689,11 @@
         <v>229</v>
       </c>
       <c r="C68" s="90" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D68" s="90"/>
       <c r="E68" s="50" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F68" s="91"/>
     </row>
@@ -10706,11 +10705,11 @@
         <v>231</v>
       </c>
       <c r="C69" s="90" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D69" s="90"/>
       <c r="E69" s="50" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F69" s="91"/>
     </row>
@@ -10722,11 +10721,11 @@
         <v>233</v>
       </c>
       <c r="C70" s="90" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D70" s="90"/>
       <c r="E70" s="50" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F70" s="91"/>
     </row>
@@ -10738,11 +10737,11 @@
         <v>235</v>
       </c>
       <c r="C71" s="90" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D71" s="90"/>
       <c r="E71" s="36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F71" s="91"/>
     </row>
@@ -10754,11 +10753,11 @@
         <v>237</v>
       </c>
       <c r="C72" s="90" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D72" s="90"/>
       <c r="E72" s="50" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F72" s="91"/>
     </row>
@@ -10782,15 +10781,15 @@
       <c r="A74" s="94" t="s">
         <v>242</v>
       </c>
-      <c r="B74" s="117" t="s">
-        <v>267</v>
+      <c r="B74" s="115" t="s">
+        <v>265</v>
       </c>
       <c r="C74" s="102" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D74" s="97"/>
       <c r="E74" s="99" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="F74" s="4"/>
     </row>
@@ -10799,46 +10798,46 @@
         <v>243</v>
       </c>
       <c r="B75" s="94" t="s">
-        <v>244</v>
+        <v>266</v>
       </c>
       <c r="C75" s="100" t="s">
         <v>24</v>
       </c>
       <c r="D75" s="97"/>
       <c r="E75" s="101" t="s">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="F75" s="4"/>
     </row>
     <row r="76" spans="1:6" ht="194.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="94" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B76" s="102" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C76" s="95" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D76" s="97"/>
       <c r="E76" s="99" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="F76" s="4"/>
     </row>
     <row r="77" spans="1:6" ht="134.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="94" t="s">
+        <v>245</v>
+      </c>
+      <c r="B77" s="96" t="s">
+        <v>246</v>
+      </c>
+      <c r="C77" s="103" t="s">
         <v>247</v>
-      </c>
-      <c r="B77" s="96" t="s">
-        <v>248</v>
-      </c>
-      <c r="C77" s="103" t="s">
-        <v>249</v>
       </c>
       <c r="D77" s="97"/>
       <c r="E77" s="99" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F77" s="4"/>
     </row>
